--- a/dcf/NOW.xlsx
+++ b/dcf/NOW.xlsx
@@ -195,7 +195,7 @@
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -442,7 +442,7 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>User-edited — overridden from Opus 16.0x</t>
+        <t>User-edited — overridden from Opus 16.0x on 2026-07-07</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1140,130 +1140,130 @@
       <c r="A5" s="53" t="n">
         <v>15.5</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>107.264335379046</v>
+      <c r="B5" s="54" t="n">
+        <v>87.23109104828568</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>102.7771250468047</v>
+        <v>83.63077242939318</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>98.50826036799771</v>
+        <v>80.20521205727881</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>94.44606687965471</v>
+        <v>76.94507773872843</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>90.57954737819792</v>
+        <v>73.84157827312768</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>86.89833965121234</v>
+        <v>70.88642970360065</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>83.39267702910062</v>
+        <v>68.07182381902254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
         <v>16.5</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>112.6743289483212</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>107.9393965020805</v>
+      <c r="B6" s="54" t="n">
+        <v>91.54542004281869</v>
+      </c>
+      <c r="C6" s="54" t="n">
+        <v>87.74754948872901</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>103.4352300824125</v>
+        <v>84.13434210556711</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>99.14947897002578</v>
+        <v>80.69592640331265</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>95.070509412969</v>
+        <v>77.42300355059908</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>91.18735985883572</v>
+        <v>74.30681163251423</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>87.4896991746803</v>
+        <v>71.33909229311176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
         <v>17.5</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>118.0843225175964</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>113.1016679573563</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>108.3621997968272</v>
+      <c r="B7" s="54" t="n">
+        <v>95.85974903735175</v>
+      </c>
+      <c r="C7" s="54" t="n">
+        <v>91.86432654806484</v>
+      </c>
+      <c r="D7" s="54" t="n">
+        <v>88.0634721538554</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>103.8528910603969</v>
+        <v>84.44677506789685</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>99.5614714477401</v>
+        <v>81.00442882807046</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>95.47638006645911</v>
+        <v>77.72719356142781</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>91.58672132026</v>
+        <v>74.60636076720098</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
         <v>18.5</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>123.4943160868716</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>118.2639394126322</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>113.289169511242</v>
+      <c r="B8" s="54" t="n">
+        <v>100.1740780318848</v>
+      </c>
+      <c r="C8" s="54" t="n">
+        <v>95.98110360740067</v>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>91.9926022021437</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>108.5563031507679</v>
+        <v>88.19762373248106</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>104.0524334825112</v>
+        <v>84.58585410554187</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>99.76540027408251</v>
+        <v>81.14757549034138</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>95.68374346583968</v>
+        <v>77.8736292412902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
         <v>19.5</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>128.9043096561469</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>123.4262108679079</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>118.2161392256567</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>113.259715241139</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>108.5433955172823</v>
+      <c r="B9" s="54" t="n">
+        <v>104.4884070264178</v>
+      </c>
+      <c r="C9" s="54" t="n">
+        <v>100.0978806667365</v>
+      </c>
+      <c r="D9" s="54" t="n">
+        <v>95.92173225043202</v>
+      </c>
+      <c r="E9" s="54" t="n">
+        <v>91.9484723970653</v>
+      </c>
+      <c r="F9" s="54" t="n">
+        <v>88.16727938301327</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>104.0544204817059</v>
+        <v>84.56795741925498</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>99.78076561141934</v>
+        <v>81.14089771537942</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>20.5</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>134.3143032254221</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>128.5884823231838</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>123.1431089400715</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>117.9631273315101</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>113.0343575520534</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>108.3434406893293</v>
+        <v>108.8027360209508</v>
+      </c>
+      <c r="C10" s="54" t="n">
+        <v>104.2146577260724</v>
+      </c>
+      <c r="D10" s="54" t="n">
+        <v>99.8508622987203</v>
+      </c>
+      <c r="E10" s="54" t="n">
+        <v>95.69932106164951</v>
+      </c>
+      <c r="F10" s="54" t="n">
+        <v>91.74870466048468</v>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>87.98833934816857</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>103.877787756999</v>
+        <v>84.40816618946864</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>21.5</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>139.7242967946973</v>
+        <v>113.1170650154839</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>133.7507537784596</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>128.0700786544863</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>122.6665394218812</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>117.5253195868245</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>112.6324608969527</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>107.9748099025787</v>
+        <v>108.3314347854082</v>
+      </c>
+      <c r="D11" s="54" t="n">
+        <v>103.7799923470086</v>
+      </c>
+      <c r="E11" s="54" t="n">
+        <v>99.45016972623372</v>
+      </c>
+      <c r="F11" s="54" t="n">
+        <v>95.33012993795607</v>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>91.40872127708214</v>
+      </c>
+      <c r="H11" s="54" t="n">
+        <v>87.67543466355787</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.7345894845766314</v>
+        <v>0.7326267767093528</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>108.5563031507679</v>
+        <v>88.19762373248106</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>151.1730307931065</v>
+        <v>119.9453194515181</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>76.61527910338062</v>
+        <v>63.78354967058681</v>
       </c>
     </row>
     <row r="59">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="F34" s="31" t="inlineStr">
         <is>
-          <t>overridden from Opus 16.0x</t>
+          <t>overridden from Opus 16.0x on 2026-07-07</t>
         </is>
       </c>
     </row>
